--- a/iwpb-sg-dashboard/sample/IWPB_SG_Driller_CIB_style.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_SG_Driller_CIB_style.xlsx
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.4</v>
+        <v>37.3</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.5</v>
+        <v>77.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>29.2</v>
+        <v>350.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.4</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="7">
@@ -1011,16 +1011,16 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.3</v>
+        <v>33.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.6</v>
+        <v>34.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>13.9</v>
+        <v>41.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>71.8</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.7</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1160,13 +1160,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.3</v>
+        <v>123.2</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.5</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="9">
@@ -1282,7 +1282,7 @@
         <v>19.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>34.7</v>
+        <v>104</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1291,16 +1291,16 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>25.1</v>
+        <v>75.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>22.3</v>
+        <v>133.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>180.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>15.6</v>
+        <v>187.5</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1419,28 +1419,28 @@
         <v>17.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.1</v>
+        <v>51.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>22.8</v>
+        <v>136.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.7</v>
+        <v>31.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>30.5</v>
+        <v>365.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.699999999999999</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="11">
@@ -1556,7 +1556,7 @@
         <v>35.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.2</v>
+        <v>33.6</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1565,19 +1565,19 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>14.1</v>
+        <v>42.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>37.2</v>
+        <v>222.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>42.8</v>
+        <v>513.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.4</v>
+        <v>88.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>45.1</v>
+        <v>541.3</v>
       </c>
     </row>
     <row r="12">
@@ -1693,25 +1693,25 @@
         <v>5.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.9</v>
+        <v>26.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>22.3</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>9.1</v>
+        <v>27.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>72.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -1830,28 +1830,28 @@
         <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.6</v>
+        <v>30.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.6</v>
+        <v>31.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="14">
@@ -1967,28 +1967,28 @@
         <v>11.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>25.3</v>
+        <v>75.8</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>53.2</v>
+        <v>159.7</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>41.1</v>
+        <v>246.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>36.7</v>
+        <v>440.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>37.7</v>
+        <v>452.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>42.6</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15">
@@ -2104,28 +2104,28 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.6</v>
+        <v>55.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.7</v>
+        <v>56.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>57.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>8.4</v>
+        <v>25.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>28.7</v>
+        <v>172.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>19.1</v>
+        <v>229.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.4</v>
+        <v>209.1</v>
       </c>
       <c r="AI15" t="n">
-        <v>37.9</v>
+        <v>454.4</v>
       </c>
     </row>
     <row r="16">
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>26.1</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2253,13 +2253,13 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>25.9</v>
+        <v>155.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.7</v>
+        <v>164.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>25.1</v>
+        <v>301.3</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2378,28 +2378,28 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.699999999999999</v>
+        <v>29</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>34.2</v>
+        <v>102.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>32.4</v>
+        <v>97.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>26.4</v>
+        <v>158.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>30.6</v>
+        <v>367.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>24.6</v>
+        <v>295.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="18">
@@ -2515,28 +2515,28 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>25.9</v>
+        <v>77.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>25</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>29.5</v>
+        <v>88.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>22.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AF18" t="n">
-        <v>25.8</v>
+        <v>155.1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>25.3</v>
+        <v>303.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="19">
@@ -2652,25 +2652,25 @@
         <v>17</v>
       </c>
       <c r="AB19" t="n">
-        <v>13.3</v>
+        <v>39.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>13.3</v>
+        <v>40</v>
       </c>
       <c r="AD19" t="n">
-        <v>11.6</v>
+        <v>34.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>25.2</v>
+        <v>75.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>5.2</v>
+        <v>31.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>35.1</v>
+        <v>420.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.2</v>
+        <v>217.9</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2795,14 +2795,14 @@
         <v>-27.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>-23.3</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-37.1</v>
+        <v>-111.4</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>(29.2)</t>
+          <t>(87.7)</t>
         </is>
       </c>
       <c r="AE20" t="n">
@@ -2812,14 +2812,14 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>-31.7</v>
+        <v>-380.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>-29.8</v>
+        <v>-357.3</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>(26.0)</t>
+          <t>(311.8)</t>
         </is>
       </c>
     </row>
@@ -2936,19 +2936,19 @@
         <v>-18</v>
       </c>
       <c r="AB21" t="n">
-        <v>-21.2</v>
+        <v>-63.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-16.3</v>
+        <v>-48.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>-28.4</v>
+        <v>-85.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>-19.7</v>
+        <v>-59.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>-22.7</v>
+        <v>-136.5</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3079,28 +3079,28 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>(20.2)</t>
+          <t>(60.6)</t>
         </is>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>(26.8)</t>
+          <t>(160.6)</t>
         </is>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>-32.8</v>
+        <v>-393.8</v>
       </c>
       <c r="AI22" t="n">
-        <v>-29.5</v>
+        <v>-354.5</v>
       </c>
     </row>
     <row r="23">
@@ -3216,24 +3216,24 @@
         <v>-14.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>-25.2</v>
+        <v>-75.5</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>(30.5)</t>
+          <t>(91.4)</t>
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>-24.5</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>-41.3</v>
+        <v>-495.8</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3356,11 +3356,11 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>(26.4)</t>
+          <t>(79.1)</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>-30.6</v>
+        <v>-91.8</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3369,11 +3369,11 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-29.5</v>
+        <v>-176.9</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>(25.3)</t>
+          <t>(303.9)</t>
         </is>
       </c>
       <c r="AH24" t="n">
@@ -3496,7 +3496,7 @@
         <v>-12.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>-22.2</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3505,21 +3505,21 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-12.2</v>
+        <v>-36.7</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>(36.7)</t>
+          <t>(220.1)</t>
         </is>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>-23</v>
+        <v>-276.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>-43.7</v>
+        <v>-524.2</v>
       </c>
     </row>
     <row r="26">
@@ -3639,28 +3639,28 @@
         <v>-28.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>-25.3</v>
+        <v>-75.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-28.7</v>
+        <v>-86.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>-27.2</v>
+        <v>-81.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>-30.3</v>
+        <v>-91</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>-22.5</v>
+        <v>-270.1</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>-23.7</v>
+        <v>-284</v>
       </c>
     </row>
     <row r="27">
@@ -3784,24 +3784,24 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>-28.3</v>
+        <v>-85</v>
       </c>
       <c r="AE27" t="n">
-        <v>-21.9</v>
+        <v>-65.59999999999999</v>
       </c>
       <c r="AF27" t="n">
-        <v>-18.3</v>
+        <v>-110</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>(10.1)</t>
+          <t>(121.0)</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-10.2</v>
+        <v>-122</v>
       </c>
       <c r="AI27" t="n">
-        <v>-1.2</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="28">
@@ -3921,27 +3921,27 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>(12.0)</t>
+          <t>(36.0)</t>
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>-7.3</v>
+        <v>-21.8</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>-12.4</v>
+        <v>-74.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>-12</v>
+        <v>-143.9</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>(12.6)</t>
+          <t>(151.2)</t>
         </is>
       </c>
     </row>
@@ -4062,30 +4062,30 @@
         <v>-54.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>-60.1</v>
+        <v>-180.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-25</v>
+        <v>-75.09999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>-12.5</v>
+        <v>-37.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>-41.8</v>
+        <v>-125.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>-22.6</v>
+        <v>-135.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>-19.4</v>
+        <v>-232.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>(31.2)</t>
+          <t>(374.1)</t>
         </is>
       </c>
       <c r="AI29" t="n">
-        <v>-51</v>
+        <v>-611.4</v>
       </c>
     </row>
     <row r="30">
@@ -4218,20 +4218,20 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>-23</v>
+        <v>-69</v>
       </c>
       <c r="AF30" t="n">
-        <v>-17.1</v>
+        <v>-102.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>-14.1</v>
+        <v>-169.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>-13.3</v>
+        <v>-159</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>(18.7)</t>
+          <t>(223.9)</t>
         </is>
       </c>
     </row>
@@ -4361,24 +4361,24 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>-40.6</v>
+        <v>-121.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>-23.2</v>
+        <v>-69.5</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>-56.6</v>
+        <v>-339.8</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>(27.2)</t>
+          <t>(326.9)</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>-20.1</v>
+        <v>-241.3</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4502,31 +4502,31 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>(6.0)</t>
+          <t>(18.1)</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>(15.5)</t>
+          <t>(46.4)</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>-17.8</v>
+        <v>-53.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>-13</v>
+        <v>-39</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>-8.699999999999999</v>
+        <v>-104</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>-10.7</v>
+        <v>-128.5</v>
       </c>
     </row>
     <row r="33">
@@ -4648,16 +4648,16 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>(20.7)</t>
+          <t>(62.2)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>(19.4)</t>
+          <t>(58.3)</t>
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4666,11 +4666,11 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>-22.5</v>
+        <v>-269.6</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>(23.5)</t>
+          <t>(282.3)</t>
         </is>
       </c>
     </row>
@@ -4787,13 +4787,13 @@
         <v>37.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>20.7</v>
+        <v>62.1</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>37.1</v>
+        <v>111.2</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4805,10 +4805,10 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>45</v>
+        <v>539.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>6.1</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -4924,28 +4924,28 @@
         <v>19.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>52.9</v>
+        <v>158.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>46.8</v>
+        <v>140.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>36.2</v>
+        <v>108.6</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>23.8</v>
+        <v>142.9</v>
       </c>
       <c r="AG35" t="n">
-        <v>55.8</v>
+        <v>669.9</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>34.9</v>
+        <v>419.3</v>
       </c>
     </row>
     <row r="36">
@@ -5070,19 +5070,19 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.8</v>
+        <v>33.4</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.9</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="37">
@@ -5198,25 +5198,25 @@
         <v>50.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>54.7</v>
+        <v>164</v>
       </c>
       <c r="AC37" t="n">
-        <v>37.2</v>
+        <v>111.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>35.1</v>
+        <v>105.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>52.6</v>
+        <v>157.9</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>44.3</v>
+        <v>531</v>
       </c>
       <c r="AH37" t="n">
-        <v>24.9</v>
+        <v>299.2</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5335,10 +5335,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>33.6</v>
+        <v>100.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.6</v>
+        <v>31.9</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5350,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>66</v>
+        <v>792</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5475,19 +5475,19 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.7</v>
+        <v>35</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>15.3</v>
+        <v>46</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>18</v>
+        <v>216.3</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
@@ -5609,28 +5609,28 @@
         <v>4.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.3</v>
+        <v>21.9</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE40" t="n">
-        <v>5.6</v>
+        <v>16.7</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>6.8</v>
+        <v>81.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>6.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AI40" t="n">
-        <v>5.2</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="41">
@@ -5746,16 +5746,16 @@
         <v>30.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>18.5</v>
+        <v>55.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>28.4</v>
+        <v>85.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE41" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>20.4</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="42">
@@ -5883,28 +5883,28 @@
         <v>22.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>24.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AC42" t="n">
-        <v>35.4</v>
+        <v>106.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>22.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="AG42" t="n">
-        <v>15.4</v>
+        <v>185</v>
       </c>
       <c r="AH42" t="n">
-        <v>15.5</v>
+        <v>186.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>28.7</v>
+        <v>344.6</v>
       </c>
     </row>
     <row r="43">
@@ -6020,28 +6020,28 @@
         <v>36.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>10</v>
+        <v>29.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>36.5</v>
+        <v>109.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="AE43" t="n">
-        <v>52.4</v>
+        <v>157.2</v>
       </c>
       <c r="AF43" t="n">
-        <v>46.3</v>
+        <v>277.6</v>
       </c>
       <c r="AG43" t="n">
-        <v>29.2</v>
+        <v>350.3</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>54.9</v>
+        <v>659.4</v>
       </c>
     </row>
     <row r="44">
@@ -6157,28 +6157,28 @@
         <v>13.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>23.8</v>
+        <v>71.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>16.6</v>
+        <v>49.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>12.5</v>
+        <v>74.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>16.2</v>
+        <v>194.7</v>
       </c>
       <c r="AH44" t="n">
-        <v>13.1</v>
+        <v>156.7</v>
       </c>
       <c r="AI44" t="n">
-        <v>20.6</v>
+        <v>246.9</v>
       </c>
     </row>
     <row r="45">
@@ -6294,28 +6294,28 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>23.9</v>
+        <v>71.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>16.9</v>
+        <v>50.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>22.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AE45" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="AF45" t="n">
-        <v>25.6</v>
+        <v>153.8</v>
       </c>
       <c r="AG45" t="n">
-        <v>28.3</v>
+        <v>339.1</v>
       </c>
       <c r="AH45" t="n">
-        <v>15.8</v>
+        <v>189.1</v>
       </c>
       <c r="AI45" t="n">
-        <v>20</v>
+        <v>240.5</v>
       </c>
     </row>
     <row r="46">
@@ -6431,7 +6431,7 @@
         <v>20.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>45.3</v>
+        <v>136</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6440,19 +6440,19 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>57.8</v>
+        <v>173.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>48.7</v>
+        <v>292.4</v>
       </c>
       <c r="AG46" t="n">
-        <v>41.2</v>
+        <v>494.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>68.2</v>
+        <v>818.3</v>
       </c>
       <c r="AI46" t="n">
-        <v>6.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
@@ -6571,19 +6571,19 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.8</v>
+        <v>11.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>9.4</v>
+        <v>28.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>7.2</v>
+        <v>21.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>6.2</v>
+        <v>37.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>10.6</v>
+        <v>127.5</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -6708,25 +6708,25 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>29</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>15.8</v>
+        <v>47.3</v>
       </c>
       <c r="AF48" t="n">
-        <v>33.9</v>
+        <v>203.2</v>
       </c>
       <c r="AG48" t="n">
-        <v>26.1</v>
+        <v>313.7</v>
       </c>
       <c r="AH48" t="n">
-        <v>16.1</v>
+        <v>193.4</v>
       </c>
       <c r="AI48" t="n">
-        <v>16.5</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="49">
@@ -6842,28 +6842,28 @@
         <v>17.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>10.8</v>
+        <v>32.3</v>
       </c>
       <c r="AC49" t="n">
-        <v>5</v>
+        <v>14.9</v>
       </c>
       <c r="AD49" t="n">
-        <v>13</v>
+        <v>38.9</v>
       </c>
       <c r="AE49" t="n">
-        <v>11.6</v>
+        <v>34.9</v>
       </c>
       <c r="AF49" t="n">
-        <v>8.5</v>
+        <v>51.1</v>
       </c>
       <c r="AG49" t="n">
-        <v>16.1</v>
+        <v>192.7</v>
       </c>
       <c r="AH49" t="n">
-        <v>2</v>
+        <v>23.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.1</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="50">
@@ -6982,25 +6982,25 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.9</v>
+        <v>26.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>16.9</v>
+        <v>50.8</v>
       </c>
       <c r="AE50" t="n">
-        <v>13.1</v>
+        <v>39.4</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>29.5</v>
+        <v>354.4</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>11.6</v>
+        <v>139.7</v>
       </c>
     </row>
     <row r="51">
@@ -7126,23 +7126,23 @@
         <v>-20.4</v>
       </c>
       <c r="AB51" t="n">
-        <v>-26.8</v>
+        <v>-80.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>-22.2</v>
+        <v>-66.5</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>-26</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="AF51" t="n">
-        <v>-22.6</v>
+        <v>-135.4</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>(30.5)</t>
+          <t>(365.9)</t>
         </is>
       </c>
       <c r="AH51" t="n">
@@ -7265,24 +7265,24 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>-13.1</v>
+        <v>-39.2</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>(13.9)</t>
+          <t>(41.6)</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>-18.9</v>
+        <v>-56.8</v>
       </c>
       <c r="AE52" t="n">
-        <v>-12.5</v>
+        <v>-37.6</v>
       </c>
       <c r="AF52" t="n">
-        <v>-9.800000000000001</v>
+        <v>-58.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>-11.3</v>
+        <v>-135.1</v>
       </c>
       <c r="AH52" t="n">
         <v>0</v>
@@ -7410,30 +7410,30 @@
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>-4.4</v>
+        <v>-13.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>-14.3</v>
+        <v>-43</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>(11.4)</t>
+          <t>(34.1)</t>
         </is>
       </c>
       <c r="AF53" t="n">
-        <v>-9.800000000000001</v>
+        <v>-58.6</v>
       </c>
       <c r="AG53" t="n">
-        <v>-13.3</v>
+        <v>-159.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>-13</v>
+        <v>-156.6</v>
       </c>
       <c r="AI53" t="n">
-        <v>-12.7</v>
+        <v>-152.3</v>
       </c>
     </row>
     <row r="54">
@@ -7551,7 +7551,7 @@
         <v>-5.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>-4.2</v>
+        <v>-12.6</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7560,20 +7560,20 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>-3.2</v>
+        <v>-9.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>-8.4</v>
+        <v>-50.3</v>
       </c>
       <c r="AG54" t="n">
-        <v>-8</v>
+        <v>-95.7</v>
       </c>
       <c r="AH54" t="n">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>(4.4)</t>
+          <t>(53.2)</t>
         </is>
       </c>
     </row>
@@ -7698,13 +7698,13 @@
         <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>-33.8</v>
+        <v>-101.4</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>-45.4</v>
+        <v>-272.3</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>-39.7</v>
+        <v>-476.4</v>
       </c>
     </row>
     <row r="56">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>(17.5)</t>
+          <t>(52.4)</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>(43.5)</t>
+          <t>(130.4)</t>
         </is>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>-39.7</v>
+        <v>-119.2</v>
       </c>
       <c r="AF56" t="n">
-        <v>-23.1</v>
+        <v>-138.9</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>-29.6</v>
+        <v>-355.3</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>(35.9)</t>
+          <t>(430.5)</t>
         </is>
       </c>
     </row>
@@ -7981,14 +7981,14 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>(18.7)</t>
+          <t>(56.2)</t>
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>-16.9</v>
+        <v>-50.6</v>
       </c>
       <c r="AD57" t="n">
-        <v>-7.1</v>
+        <v>-21.3</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7997,10 +7997,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>-11.7</v>
+        <v>-140</v>
       </c>
       <c r="AH57" t="n">
-        <v>-12</v>
+        <v>-144.6</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -8128,29 +8128,29 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>(4.2)</t>
+          <t>(12.5)</t>
         </is>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>-15.5</v>
+        <v>-46.6</v>
       </c>
       <c r="AE58" t="n">
-        <v>-11</v>
+        <v>-32.9</v>
       </c>
       <c r="AF58" t="n">
-        <v>-16.5</v>
+        <v>-98.7</v>
       </c>
       <c r="AG58" t="n">
-        <v>-17.2</v>
+        <v>-206.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>-9.800000000000001</v>
+        <v>-118.1</v>
       </c>
       <c r="AI58" t="n">
-        <v>-17.1</v>
+        <v>-205.1</v>
       </c>
     </row>
     <row r="59">
@@ -8269,17 +8269,17 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>(17.6)</t>
+          <t>(52.8)</t>
         </is>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>-7.9</v>
+        <v>-23.7</v>
       </c>
       <c r="AE59" t="n">
-        <v>-13.8</v>
+        <v>-41.3</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -8291,7 +8291,7 @@
         <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>-16.8</v>
+        <v>-201.6</v>
       </c>
     </row>
     <row r="60">
@@ -8418,23 +8418,23 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>(23.2)</t>
+          <t>(69.7)</t>
         </is>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>-16</v>
+        <v>-96.09999999999999</v>
       </c>
       <c r="AG60" t="n">
-        <v>-30.8</v>
+        <v>-370.1</v>
       </c>
       <c r="AH60" t="n">
-        <v>-14.8</v>
+        <v>-177.1</v>
       </c>
       <c r="AI60" t="n">
-        <v>-18.5</v>
+        <v>-221.8</v>
       </c>
     </row>
     <row r="61">
@@ -8554,30 +8554,30 @@
         <v>-14.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>-12.6</v>
+        <v>-37.9</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>(16.3)</t>
+          <t>(49.0)</t>
         </is>
       </c>
       <c r="AE61" t="n">
-        <v>-13.8</v>
+        <v>-41.3</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>-5.8</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="AH61" t="n">
-        <v>-10</v>
+        <v>-119.9</v>
       </c>
       <c r="AI61" t="n">
-        <v>-8.1</v>
+        <v>-97.7</v>
       </c>
     </row>
     <row r="62">
@@ -8697,22 +8697,22 @@
         <v>-10.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>-13.6</v>
+        <v>-40.7</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>-15.2</v>
+        <v>-45.5</v>
       </c>
       <c r="AE62" t="n">
-        <v>-11.2</v>
+        <v>-33.5</v>
       </c>
       <c r="AF62" t="n">
-        <v>-13.3</v>
+        <v>-79.8</v>
       </c>
       <c r="AG62" t="n">
-        <v>-6.9</v>
+        <v>-83.3</v>
       </c>
       <c r="AH62" t="n">
         <v>0</v>
@@ -8835,29 +8835,29 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>(12.6)</t>
+          <t>(37.7)</t>
         </is>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>-0.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AE63" t="n">
-        <v>-8.300000000000001</v>
+        <v>-24.9</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>-11.9</v>
+        <v>-142.5</v>
       </c>
       <c r="AH63" t="n">
-        <v>-9.4</v>
+        <v>-112.9</v>
       </c>
       <c r="AI63" t="n">
-        <v>-4</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="64">
@@ -8978,14 +8978,14 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>-9</v>
+        <v>-27.1</v>
       </c>
       <c r="AD64" t="n">
-        <v>-15.6</v>
+        <v>-46.9</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>(35.4)</t>
+          <t>(106.3)</t>
         </is>
       </c>
       <c r="AF64" t="n">
@@ -8993,14 +8993,14 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>(26.1)</t>
+          <t>(313.3)</t>
         </is>
       </c>
       <c r="AH64" t="n">
         <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>-18</v>
+        <v>-216.1</v>
       </c>
     </row>
     <row r="65">
@@ -9118,29 +9118,29 @@
         <v>-19.6</v>
       </c>
       <c r="AB65" t="n">
-        <v>-13.3</v>
+        <v>-39.9</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>(9.3)</t>
+          <t>(27.9)</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>-24.6</v>
+        <v>-73.8</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>(13.1)</t>
+          <t>(39.3)</t>
         </is>
       </c>
       <c r="AF65" t="n">
-        <v>-30.5</v>
+        <v>-183.3</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>-21.4</v>
+        <v>-257.3</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -9259,33 +9259,33 @@
         <v>-2.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>-3.7</v>
+        <v>-11.1</v>
       </c>
       <c r="AC66" t="n">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>(1.9)</t>
+          <t>(5.8)</t>
         </is>
       </c>
       <c r="AE66" t="n">
-        <v>-2.6</v>
+        <v>-7.8</v>
       </c>
       <c r="AF66" t="n">
-        <v>-1.4</v>
+        <v>-8.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>-3</v>
+        <v>-36.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>(3.3)</t>
+          <t>(39.2)</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>(5.5)</t>
+          <t>(65.9)</t>
         </is>
       </c>
     </row>
@@ -9405,25 +9405,25 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>7.5</v>
+        <v>22.6</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>22.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AF67" t="n">
-        <v>40.6</v>
+        <v>243.7</v>
       </c>
       <c r="AG67" t="n">
-        <v>45.3</v>
+        <v>543.3</v>
       </c>
       <c r="AH67" t="n">
         <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>20.7</v>
+        <v>248.7</v>
       </c>
     </row>
     <row r="68">
@@ -9542,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9551,16 +9551,16 @@
         <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>8.300000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="AG68" t="n">
-        <v>6.3</v>
+        <v>75.5</v>
       </c>
       <c r="AH68" t="n">
         <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>7.2</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="69">
@@ -9676,28 +9676,28 @@
         <v>6.4</v>
       </c>
       <c r="AB69" t="n">
-        <v>11.3</v>
+        <v>33.9</v>
       </c>
       <c r="AC69" t="n">
-        <v>12.6</v>
+        <v>37.7</v>
       </c>
       <c r="AD69" t="n">
-        <v>13.4</v>
+        <v>40.3</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>9.4</v>
+        <v>56.6</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>9.6</v>
+        <v>115.3</v>
       </c>
       <c r="AI69" t="n">
-        <v>9.300000000000001</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="70">
@@ -9813,28 +9813,28 @@
         <v>16.4</v>
       </c>
       <c r="AB70" t="n">
-        <v>15.9</v>
+        <v>47.8</v>
       </c>
       <c r="AC70" t="n">
-        <v>7.1</v>
+        <v>21.2</v>
       </c>
       <c r="AD70" t="n">
-        <v>23.7</v>
+        <v>71.2</v>
       </c>
       <c r="AE70" t="n">
-        <v>22.6</v>
+        <v>67.8</v>
       </c>
       <c r="AF70" t="n">
-        <v>26.1</v>
+        <v>156.9</v>
       </c>
       <c r="AG70" t="n">
-        <v>20.4</v>
+        <v>245</v>
       </c>
       <c r="AH70" t="n">
-        <v>26.7</v>
+        <v>320.5</v>
       </c>
       <c r="AI70" t="n">
-        <v>9.4</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="71">
@@ -9959,19 +9959,19 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>35.7</v>
+        <v>107</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>24.2</v>
+        <v>290</v>
       </c>
       <c r="AH71" t="n">
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>7.9</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="72">
@@ -10087,28 +10087,28 @@
         <v>25.3</v>
       </c>
       <c r="AB72" t="n">
-        <v>14.7</v>
+        <v>44.2</v>
       </c>
       <c r="AC72" t="n">
-        <v>14.4</v>
+        <v>43.3</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>8.699999999999999</v>
+        <v>26</v>
       </c>
       <c r="AF72" t="n">
-        <v>14</v>
+        <v>83.7</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>15.5</v>
+        <v>186.5</v>
       </c>
       <c r="AI72" t="n">
-        <v>14.2</v>
+        <v>170.3</v>
       </c>
     </row>
     <row r="73">
@@ -10236,16 +10236,16 @@
         <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>45.4</v>
+        <v>272.4</v>
       </c>
       <c r="AG73" t="n">
-        <v>40.6</v>
+        <v>486.7</v>
       </c>
       <c r="AH73" t="n">
-        <v>39</v>
+        <v>468.2</v>
       </c>
       <c r="AI73" t="n">
-        <v>40.2</v>
+        <v>482.1</v>
       </c>
     </row>
     <row r="74">
@@ -10361,22 +10361,22 @@
         <v>15.5</v>
       </c>
       <c r="AB74" t="n">
-        <v>8.9</v>
+        <v>26.6</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>6.4</v>
+        <v>19.1</v>
       </c>
       <c r="AF74" t="n">
-        <v>4.8</v>
+        <v>28.6</v>
       </c>
       <c r="AG74" t="n">
-        <v>12.3</v>
+        <v>147.1</v>
       </c>
       <c r="AH74" t="n">
         <v>0</v>
@@ -10498,25 +10498,25 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>24.3</v>
+        <v>73</v>
       </c>
       <c r="AC75" t="n">
-        <v>27.7</v>
+        <v>83.2</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>28.3</v>
+        <v>84.8</v>
       </c>
       <c r="AF75" t="n">
-        <v>40.8</v>
+        <v>244.6</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>52.5</v>
+        <v>629.8</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -10635,25 +10635,25 @@
         <v>24.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>6.3</v>
+        <v>18.8</v>
       </c>
       <c r="AC76" t="n">
-        <v>23.4</v>
+        <v>70.2</v>
       </c>
       <c r="AD76" t="n">
-        <v>38.3</v>
+        <v>115</v>
       </c>
       <c r="AE76" t="n">
-        <v>11.4</v>
+        <v>34.3</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>32</v>
+        <v>383.9</v>
       </c>
       <c r="AH76" t="n">
-        <v>32.6</v>
+        <v>390.9</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10778,22 +10778,22 @@
         <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>11.2</v>
+        <v>33.6</v>
       </c>
       <c r="AE77" t="n">
         <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>9.5</v>
+        <v>57</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>5.5</v>
+        <v>65.7</v>
       </c>
       <c r="AI77" t="n">
-        <v>11.2</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="78">
@@ -10909,25 +10909,25 @@
         <v>33.2</v>
       </c>
       <c r="AB78" t="n">
-        <v>39.3</v>
+        <v>117.8</v>
       </c>
       <c r="AC78" t="n">
-        <v>21.6</v>
+        <v>64.7</v>
       </c>
       <c r="AD78" t="n">
-        <v>22</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AE78" t="n">
-        <v>44.1</v>
+        <v>132.4</v>
       </c>
       <c r="AF78" t="n">
-        <v>48.1</v>
+        <v>288.5</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>38.7</v>
+        <v>464.2</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -11046,13 +11046,13 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>26.6</v>
+        <v>79.7</v>
       </c>
       <c r="AC79" t="n">
-        <v>26.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AD79" t="n">
-        <v>38.5</v>
+        <v>115.6</v>
       </c>
       <c r="AE79" t="n">
         <v>0</v>
@@ -11061,10 +11061,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>14.4</v>
+        <v>172.2</v>
       </c>
       <c r="AH79" t="n">
-        <v>17.6</v>
+        <v>211</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -11183,28 +11183,28 @@
         <v>1.8</v>
       </c>
       <c r="AB80" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AC80" t="n">
-        <v>4.4</v>
+        <v>13.1</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AF80" t="n">
-        <v>3</v>
+        <v>17.8</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.7</v>
+        <v>32.5</v>
       </c>
       <c r="AH80" t="n">
         <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>3.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="81">
@@ -11320,10 +11320,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>31.6</v>
+        <v>94.8</v>
       </c>
       <c r="AC81" t="n">
-        <v>20.4</v>
+        <v>61.2</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11332,13 +11332,13 @@
         <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>27.5</v>
+        <v>164.9</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>21.8</v>
+        <v>261.1</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -11457,19 +11457,19 @@
         <v>16.1</v>
       </c>
       <c r="AB82" t="n">
-        <v>6.3</v>
+        <v>18.8</v>
       </c>
       <c r="AC82" t="n">
-        <v>25.1</v>
+        <v>75.2</v>
       </c>
       <c r="AD82" t="n">
-        <v>22.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>22.4</v>
+        <v>134.3</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>24.9</v>
+        <v>299.3</v>
       </c>
     </row>
     <row r="83">
@@ -11594,25 +11594,25 @@
         <v>30.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>21</v>
+        <v>63.1</v>
       </c>
       <c r="AC83" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>22.3</v>
+        <v>67</v>
       </c>
       <c r="AF83" t="n">
-        <v>60.2</v>
+        <v>361.4</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>60.9</v>
+        <v>730.8</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11734,7 +11734,7 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>43.1</v>
+        <v>129.2</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11749,10 +11749,10 @@
         <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>4.4</v>
+        <v>53.3</v>
       </c>
       <c r="AI84" t="n">
-        <v>24.6</v>
+        <v>295.2</v>
       </c>
     </row>
     <row r="85">
@@ -11868,16 +11868,16 @@
         <v>10.9</v>
       </c>
       <c r="AB85" t="n">
-        <v>9.5</v>
+        <v>28.6</v>
       </c>
       <c r="AC85" t="n">
-        <v>9.6</v>
+        <v>28.7</v>
       </c>
       <c r="AD85" t="n">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="AE85" t="n">
-        <v>8.5</v>
+        <v>25.5</v>
       </c>
       <c r="AF85" t="n">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>12.2</v>
+        <v>145.9</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -12008,16 +12008,16 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>9.1</v>
+        <v>27.2</v>
       </c>
       <c r="AD86" t="n">
-        <v>40.5</v>
+        <v>121.5</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>41.9</v>
+        <v>251.6</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -12157,13 +12157,13 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>38.6</v>
+        <v>462.6</v>
       </c>
       <c r="AH87" t="n">
         <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>27.3</v>
+        <v>327.7</v>
       </c>
     </row>
     <row r="88">
@@ -12279,28 +12279,28 @@
         <v>1.2</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>3.3</v>
+        <v>19.6</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="AI88" t="n">
-        <v>2</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="89">
@@ -12416,28 +12416,28 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.4</v>
+        <v>14.2</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="90">
@@ -12553,19 +12553,19 @@
         <v>13.7</v>
       </c>
       <c r="AB90" t="n">
-        <v>16.8</v>
+        <v>50.4</v>
       </c>
       <c r="AC90" t="n">
-        <v>24.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AD90" t="n">
-        <v>18.3</v>
+        <v>54.9</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>37.2</v>
+        <v>223.3</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -12574,7 +12574,7 @@
         <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>46</v>
+        <v>552</v>
       </c>
     </row>
     <row r="91">
@@ -12690,16 +12690,16 @@
         <v>25.1</v>
       </c>
       <c r="AB91" t="n">
-        <v>36.3</v>
+        <v>108.8</v>
       </c>
       <c r="AC91" t="n">
-        <v>27.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>32.1</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
@@ -12711,7 +12711,7 @@
         <v>0</v>
       </c>
       <c r="AI91" t="n">
-        <v>23.9</v>
+        <v>287</v>
       </c>
     </row>
     <row r="92">
@@ -12827,25 +12827,25 @@
         <v>0.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC92" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="AF92" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="AG92" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="AH92" t="n">
-        <v>2.2</v>
+        <v>26</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12967,25 +12967,25 @@
         <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>19.7</v>
+        <v>59.1</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>16.9</v>
+        <v>50.6</v>
       </c>
       <c r="AF93" t="n">
-        <v>12.3</v>
+        <v>73.8</v>
       </c>
       <c r="AG93" t="n">
-        <v>7.2</v>
+        <v>86</v>
       </c>
       <c r="AH93" t="n">
-        <v>17.6</v>
+        <v>211.5</v>
       </c>
       <c r="AI93" t="n">
-        <v>15.8</v>
+        <v>189.1</v>
       </c>
     </row>
     <row r="94">
@@ -13101,13 +13101,13 @@
         <v>72.7</v>
       </c>
       <c r="AB94" t="n">
-        <v>37.7</v>
+        <v>113</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>57.3</v>
+        <v>171.8</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -13116,13 +13116,13 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>50.8</v>
+        <v>609.1</v>
       </c>
       <c r="AH94" t="n">
         <v>0</v>
       </c>
       <c r="AI94" t="n">
-        <v>38.8</v>
+        <v>465.8</v>
       </c>
     </row>
     <row r="95">
@@ -13238,10 +13238,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="AC95" t="n">
-        <v>3.5</v>
+        <v>10.6</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13250,10 +13250,10 @@
         <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.1</v>
+        <v>12.6</v>
       </c>
       <c r="AG95" t="n">
-        <v>5.2</v>
+        <v>61.8</v>
       </c>
       <c r="AH95" t="n">
         <v>0</v>
@@ -13375,25 +13375,25 @@
         <v>14.2</v>
       </c>
       <c r="AB96" t="n">
-        <v>40.2</v>
+        <v>120.6</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>30.1</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AE96" t="n">
-        <v>24.2</v>
+        <v>72.5</v>
       </c>
       <c r="AF96" t="n">
         <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>17.8</v>
+        <v>213.2</v>
       </c>
       <c r="AH96" t="n">
-        <v>36.4</v>
+        <v>437.2</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -13515,16 +13515,16 @@
         <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>36.8</v>
+        <v>110.5</v>
       </c>
       <c r="AD97" t="n">
-        <v>35.3</v>
+        <v>105.9</v>
       </c>
       <c r="AE97" t="n">
-        <v>28.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.9</v>
+        <v>11.2</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
         <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>32.9</v>
+        <v>394.3</v>
       </c>
     </row>
     <row r="98">
@@ -13649,7 +13649,7 @@
         <v>13.9</v>
       </c>
       <c r="AB98" t="n">
-        <v>17.8</v>
+        <v>53.3</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13658,16 +13658,16 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>9.6</v>
+        <v>28.7</v>
       </c>
       <c r="AF98" t="n">
-        <v>7.5</v>
+        <v>45.2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>22.2</v>
+        <v>266.5</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>

--- a/iwpb-sg-dashboard/sample/IWPB_SG_Driller_CIB_style.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_SG_Driller_CIB_style.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI98"/>
+  <dimension ref="A1:AI145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13673,6 +13673,6783 @@
         <v>0</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>UNMAPPDT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>-37.7</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>-38.1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>(9.7)</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="U99" t="n">
+        <v>-33</v>
+      </c>
+      <c r="V99" t="n">
+        <v>-28.6</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>(4.8)</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>(40.1)</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>(23.7)</t>
+        </is>
+      </c>
+      <c r="AA99" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>-99.40000000000001</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>-72.40000000000001</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>-86.8</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>(196.4)</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>(356.8)</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>-126.1</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>UNMAPPDT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="R100" t="n">
+        <v>-36.4</v>
+      </c>
+      <c r="S100" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="T100" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>(39.1)</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>(28.1)</t>
+        </is>
+      </c>
+      <c r="AA100" t="n">
+        <v>-52.8</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>-65.90000000000001</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>-97</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>-182.8</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>-74.09999999999999</v>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>(171.6)</t>
+        </is>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>-408.7</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PR04000002</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="V101" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="W101" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="X101" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>(19.7)</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>(33.2)</t>
+        </is>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PR04000002</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="R102" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="S102" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="T102" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="U102" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="V102" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="W102" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>(5.5)</t>
+        </is>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>(17.2)</t>
+        </is>
+      </c>
+      <c r="AD102" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>(33.5)</t>
+        </is>
+      </c>
+      <c r="AF102" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>(118.3)</t>
+        </is>
+      </c>
+      <c r="AI102" t="n">
+        <v>-144.9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Other Lending</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>(0.9)</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>(0.3)</t>
+        </is>
+      </c>
+      <c r="S103" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="T103" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="U103" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="X103" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>-17.1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>(75.9)</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>-62.8</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>(39.7)</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>-92.3</v>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>(117.0)</t>
+        </is>
+      </c>
+      <c r="AD104" t="n">
+        <v>-126.6</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>-319.3</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>-32.4</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>(25.9)</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>(25.4)</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="X105" t="n">
+        <v>-25.6</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>(20.3)</t>
+        </is>
+      </c>
+      <c r="AA105" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>-80.7</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>-93</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>-119.3</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>-321.1</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>-180.1</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>(269.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PR04030000</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Credit Cards</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Cards</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>(20.8)</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>(7.3)</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>(22.7)</t>
+        </is>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>(86.4)</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>-57.6</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>-79.59999999999999</v>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>(140.9)</t>
+        </is>
+      </c>
+      <c r="AG106" t="n">
+        <v>-294.2</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PR04060600</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Structured Products</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="R107" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="S107" t="n">
+        <v>-32.1</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>(9.5)</t>
+        </is>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="W107" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>-42.7</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>-82.8</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>-39.7</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>-241.6</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PR04060600</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Structured Products</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>-38.4</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="T108" t="n">
+        <v>-43.8</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>(33.3)</t>
+        </is>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-61.3</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>-169.9</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>-22.3</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>-194.7</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>-213</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>(22.8)</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>-24.1</v>
+      </c>
+      <c r="T109" t="n">
+        <v>-28</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="W109" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>(38.4)</t>
+        </is>
+      </c>
+      <c r="Z109" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>(72.5)</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>-35.8</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>-87.2</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>-85.8</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>(171.2)</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>(346.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="S110" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="T110" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>(10.8)</t>
+        </is>
+      </c>
+      <c r="W110" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>(15.6)</t>
+        </is>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>(8.8)</t>
+        </is>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>(60.4)</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>(91.3)</t>
+        </is>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>-190.1</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>-399.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PR05040000</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Savings and Deposit Accounts</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="T111" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>(13.3)</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>(7.0)</t>
+        </is>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>-46.5</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>-142.2</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>-159.2</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>-153.4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PR04060550</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Other products</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Total Other Products</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="T112" t="n">
+        <v>-28</v>
+      </c>
+      <c r="U112" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>(18.5)</t>
+        </is>
+      </c>
+      <c r="W112" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="X112" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>(15.8)</t>
+        </is>
+      </c>
+      <c r="AB112" t="n">
+        <v>-68.3</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>(77.3)</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>(29.7)</t>
+        </is>
+      </c>
+      <c r="AF112" t="n">
+        <v>-92.40000000000001</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PR04060550</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Other products</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Total Other Products</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>-28.6</v>
+      </c>
+      <c r="R113" t="n">
+        <v>-41</v>
+      </c>
+      <c r="S113" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="T113" t="n">
+        <v>-42.9</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>(34.4)</t>
+        </is>
+      </c>
+      <c r="V113" t="n">
+        <v>-35.7</v>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>(44.2)</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>(26.4)</t>
+        </is>
+      </c>
+      <c r="Y113" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>-100.8</v>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>(82.2)</t>
+        </is>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>(165.9)</t>
+        </is>
+      </c>
+      <c r="AG113" t="n">
+        <v>-221.8</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>-273.9</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>-301.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PR10090005</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Non Product Allocation of Corp Centre</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Non Product Results Total</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>(38.0)</t>
+        </is>
+      </c>
+      <c r="T114" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="U114" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="X114" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>-26.8</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>(69.6)</t>
+        </is>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>-67.5</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>-127.4</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>(163.9)</t>
+        </is>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MP20101000000</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Direct Costs</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PR10090005</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Non Product Allocation of Corp Centre</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Non Product Results Total</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>(14.8)</t>
+        </is>
+      </c>
+      <c r="S115" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="T115" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="U115" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>(18.0)</t>
+        </is>
+      </c>
+      <c r="X115" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>(8.2)</t>
+        </is>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>-45.2</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>-48.2</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>-53.3</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>(44.4)</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>(62.7)</t>
+        </is>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>-277.7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>UNMAPPDT</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>(21.0)</t>
+        </is>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>(16.5)</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>(42.6)</t>
+        </is>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>-90.5</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>-52.6</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>(106.4)</t>
+        </is>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>-190.3</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>-243.3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PR04000002</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>(32.0)</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>(27.7)</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>(23.1)</t>
+        </is>
+      </c>
+      <c r="U117" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>(57.2)</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>(71.8)</t>
+        </is>
+      </c>
+      <c r="AE117" t="n">
+        <v>-67.59999999999999</v>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>(104.7)</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>(173.0)</t>
+        </is>
+      </c>
+      <c r="AH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PR04000002</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R118" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="T118" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="W118" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="X118" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>(26.0)</t>
+        </is>
+      </c>
+      <c r="AB118" t="n">
+        <v>-52.1</v>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>(58.4)</t>
+        </is>
+      </c>
+      <c r="AD118" t="n">
+        <v>-58.2</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>(123.1)</t>
+        </is>
+      </c>
+      <c r="AG118" t="n">
+        <v>-138.5</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>-151.9</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>-77.90000000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Other Lending</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>-51.6</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>-59.6</v>
+      </c>
+      <c r="V119" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>-34.3</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>-61.2</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>-116.6</v>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>(115.6)</t>
+        </is>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>-141.5</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>-517.9</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-388.7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Other Lending</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>(39.7)</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>(30.3)</t>
+        </is>
+      </c>
+      <c r="X120" t="n">
+        <v>-29</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>(22.5)</t>
+        </is>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>-115.9</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>-115.7</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>-87.90000000000001</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>-64.7</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>(163.6)</t>
+        </is>
+      </c>
+      <c r="AI120" t="n">
+        <v>-430.6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>(9.6)</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>(4.8)</t>
+        </is>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="W121" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>(4.8)</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>(94.7)</t>
+        </is>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PR04030000</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Credit Cards</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cards</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>(29.1)</t>
+        </is>
+      </c>
+      <c r="S122" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>(43.5)</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>(44.0)</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>(36.9)</t>
+        </is>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>(51.9)</t>
+        </is>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>(89.0)</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>(76.3)</t>
+        </is>
+      </c>
+      <c r="AF122" t="n">
+        <v>-154.5</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-318.1</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-308.7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PR04060600</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Structured Products</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>-44.2</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>(21.8)</t>
+        </is>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>(25.2)</t>
+        </is>
+      </c>
+      <c r="Y123" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>-38.3</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>-92</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>-88</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>-116.8</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>-185</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>(433.7)</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>(238.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PR04060600</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Structured Products</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>-23</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>-33.6</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-26.3</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>(13.8)</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="U124" t="n">
+        <v>-32.5</v>
+      </c>
+      <c r="V124" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="W124" t="n">
+        <v>-31</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>(26.0)</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>(24.9)</t>
+        </is>
+      </c>
+      <c r="Z124" t="n">
+        <v>-38.2</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>(22.6)</t>
+        </is>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>-64.5</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>-55.6</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>-371.3</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>-262.3</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R125" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>-42.8</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>(32.2)</t>
+        </is>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>-168.2</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>-73.09999999999999</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>-92.5</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>-270.4</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>-39.5</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>(19.3)</t>
+        </is>
+      </c>
+      <c r="S126" t="n">
+        <v>-24.1</v>
+      </c>
+      <c r="T126" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-91.90000000000001</v>
+      </c>
+      <c r="V126" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>(44.1)</t>
+        </is>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-62.1</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>(35.0)</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>(162.8)</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>-115.8</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>(827.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PR05040000</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Savings and Deposit Accounts</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-42.2</v>
+      </c>
+      <c r="T127" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="U127" t="n">
+        <v>-37.2</v>
+      </c>
+      <c r="V127" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-32.4</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-33.9</v>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>(57.0)</t>
+        </is>
+      </c>
+      <c r="Z127" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>(31.1)</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>-139.9</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>-123.3</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-188.2</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>-766.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>PR05040000</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Savings and Deposit Accounts</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>(36.7)</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>(33.3)</t>
+        </is>
+      </c>
+      <c r="U128" t="n">
+        <v>-25</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>-38.3</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>-57.3</v>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>(20.2)</t>
+        </is>
+      </c>
+      <c r="AA128" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>(179.6)</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>-116.5</v>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>(64.4)</t>
+        </is>
+      </c>
+      <c r="AE128" t="n">
+        <v>-76.59999999999999</v>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>(243.4)</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>(415.9)</t>
+        </is>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>-163.6</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>PR04060550</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Other products</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Total Other Products</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>-45.1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>-42.1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>-35.7</v>
+      </c>
+      <c r="S129" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>(38.3)</t>
+        </is>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="X129" t="n">
+        <v>-46</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>-36.7</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>-131.7</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>-86.2</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>-181.5</v>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>(233.4)</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>(227.6)</t>
+        </is>
+      </c>
+      <c r="AH129" t="n">
+        <v>-202.8</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>(409.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PR10090005</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Non Product Allocation of Corp Centre</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Non Product Results Total</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>(21.5)</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="S130" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>(13.7)</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>(14.3)</t>
+        </is>
+      </c>
+      <c r="V130" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="W130" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>(94.0)</t>
+        </is>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-105.5</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-73.59999999999999</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>-317.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MP20102000000</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Allocated Costs</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Indirect Costs</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PR10090005</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Non Product Allocation of Corp Centre</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Non Product Results Total</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R131" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="S131" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="U131" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>(23.3)</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>(19.8)</t>
+        </is>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>-34.8</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>(114.9)</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>(80.9)</t>
+        </is>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>-228.2</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>-321.4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>UNMAPPDT</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>-22</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="W132" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="X132" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>(12.7)</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>(29.7)</t>
+        </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>-109.1</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>-90</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>-96.8</v>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>(79.2)</t>
+        </is>
+      </c>
+      <c r="AF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>-184.5</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>-280.4</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>UNMAPPDT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Unmapped Product</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>(22.8)</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>(13.2)</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>(15.1)</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>-28.3</v>
+      </c>
+      <c r="T133" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>(4.5)</t>
+        </is>
+      </c>
+      <c r="Z133" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-72.2</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-116.4</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>(109.8)</t>
+        </is>
+      </c>
+      <c r="AE133" t="n">
+        <v>-102.7</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-156.9</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-107.9</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PR04000002</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>-18</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>(13.3)</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="T134" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>(16.3)</t>
+        </is>
+      </c>
+      <c r="V134" t="n">
+        <v>-14</v>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>(16.2)</t>
+        </is>
+      </c>
+      <c r="X134" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>-43.9</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>-40.2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>(34.1)</t>
+        </is>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>-225.9</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>-108.1</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-75.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PR04000002</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>(48.6)</t>
+        </is>
+      </c>
+      <c r="R135" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-57.3</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-22</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-41.4</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>(49.0)</t>
+        </is>
+      </c>
+      <c r="AA135" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-77.5</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>(150.6)</t>
+        </is>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-164</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>-264.2</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>-200.9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Other Lending</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-65.40000000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-63.7</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-259.1</v>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>(293.1)</t>
+        </is>
+      </c>
+      <c r="AH136" t="n">
+        <v>-263.3</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>(437.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Other Lending</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>(40.5)</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-46.1</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>(20.6)</t>
+        </is>
+      </c>
+      <c r="X137" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-41.4</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>(42.2)</t>
+        </is>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-52.8</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>-67.40000000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>(114.8)</t>
+        </is>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>(33.5)</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>(15.1)</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-67.5</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-74.59999999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-188.1</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>-195.9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="T139" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="U139" t="n">
+        <v>-17</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>-18</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>(12.1)</t>
+        </is>
+      </c>
+      <c r="Y139" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>-58.1</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>-31.9</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-159.5</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>(139.6)</t>
+        </is>
+      </c>
+      <c r="AI139" t="n">
+        <v>-169.6</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PR04030000</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Credit Cards</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Cards</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>-38.7</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>-39.4</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>(53.3)</t>
+        </is>
+      </c>
+      <c r="Z140" t="n">
+        <v>-36.2</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>-57.2</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>-80.8</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>-115.5</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>-38.8</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>-204.6</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>-120.8</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>-33.8</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>-573.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PR04030000</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Credit Cards</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Cards</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>-42.7</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>(53.2)</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>-55.6</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>-32.4</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>(24.5)</t>
+        </is>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>-44.3</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>(23.7)</t>
+        </is>
+      </c>
+      <c r="AA141" t="n">
+        <v>-45.7</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>-174</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>-82.90000000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>-141.2</v>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>(122.2)</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>(297.5)</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>(463.8)</t>
+        </is>
+      </c>
+      <c r="AH141" t="n">
+        <v>-324.3</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PR05040000</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Savings and Deposit Accounts</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="T142" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="U142" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="V142" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="W142" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>(8.6)</t>
+        </is>
+      </c>
+      <c r="Z142" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>(27.8)</t>
+        </is>
+      </c>
+      <c r="AE142" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>(103.7)</t>
+        </is>
+      </c>
+      <c r="AH142" t="n">
+        <v>-96.40000000000001</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>-110.1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PR04060550</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Other products</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Total Other Products</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>(5.9)</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>(5.6)</t>
+        </is>
+      </c>
+      <c r="X143" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>-70.5</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-62.9</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-66.2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PR10090005</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Non Product Allocation of Corp Centre</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Non Product Results Total</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>RTN00008</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Premier and Wealth</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>(7.5)</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="S144" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="T144" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="W144" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>(12.8)</t>
+        </is>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>-84.2</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>-106.8</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MP30101000000</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ECL Charge</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PR10090005</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Non Product Allocation of Corp Centre</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Non Product Results Total</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>RTN00012</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Personal Banking</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Intl Wealth &amp; Premier Banking</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>(24.9)</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="S145" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="T145" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>(8.3)</t>
+        </is>
+      </c>
+      <c r="AB145" t="n">
+        <v>-48.1</v>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>(79.9)</t>
+        </is>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>(76.9)</t>
+        </is>
+      </c>
+      <c r="AF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>-297.4</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>(229.2)</t>
+        </is>
+      </c>
+      <c r="AI145" t="n">
+        <v>-317.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iwpb-sg-dashboard/sample/IWPB_SG_Driller_CIB_style.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_SG_Driller_CIB_style.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>FY-26</t>
+          <t>FY-26 Forecast</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
